--- a/utils/monday_sprint_sprint_2026-14.xlsx
+++ b/utils/monday_sprint_sprint_2026-14.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="384">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -63,384 +63,426 @@
     <t>37169</t>
   </si>
   <si>
+    <t>Fundição</t>
+  </si>
+  <si>
+    <t>Melhoria</t>
+  </si>
+  <si>
+    <t>Solicitação de serviço</t>
+  </si>
+  <si>
+    <t>Alteração em relatorio dentro do sistema "Apontamento de produção"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde, solicito a alteração no relatório de apontamento por funcionário quando "gerar o Excel". Preciso que no relatório saia o turno e o setor que cada funcionário faz parte ( inspeção END ou DIM). Motivo: Facilitar e otimizar o tempo de elaboração do relatório disponibilizado para liderança e </t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>Gerson Mendonça</t>
+  </si>
+  <si>
+    <t>Sistemas</t>
+  </si>
+  <si>
+    <t>18/05/2026</t>
+  </si>
+  <si>
+    <t>11/06/2026</t>
+  </si>
+  <si>
+    <t>Implantação</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
+  </si>
+  <si>
+    <t>Maio</t>
+  </si>
+  <si>
+    <t>37881</t>
+  </si>
+  <si>
+    <t>Almoxarifado</t>
+  </si>
+  <si>
+    <t>Automatização NF de transferência</t>
+  </si>
+  <si>
+    <t>Boa tarde! Atualmente, o processo de transferência de saldo (estoque atual e importação) é realizado de forma manual. A proposta é automatizar esse fluxo com base nas Notas Fiscais emitidas e recebidas. Hoje, o estoque de importação é controlado pela Total Comex. O objetivo é ativar uma flag por for</t>
+  </si>
+  <si>
+    <t>Alex Julio Estacio</t>
+  </si>
+  <si>
+    <t>30/04/2026</t>
+  </si>
+  <si>
+    <t>16/06/2026</t>
+  </si>
+  <si>
+    <t>Fazendo</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>38071</t>
+  </si>
+  <si>
+    <t>Logística</t>
+  </si>
+  <si>
+    <t>Avaliação de Ferramenta - LogX Narwall - Reunião</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde, Estou abrindo o chamado para avaliação da integração com API aberta da Ferramental LogX da Narwal com o sistema de Invoice. Abaixo o link da documentação enviada pela empresa. Desconheço procedimentos, gentileza informar o que há necessidade do nosso lado para avaliação. Acredito que uma </t>
+  </si>
+  <si>
+    <t>Djalma Machado</t>
+  </si>
+  <si>
+    <t>27/05/2026</t>
+  </si>
+  <si>
+    <t>A fazer</t>
+  </si>
+  <si>
+    <t>12038539869</t>
+  </si>
+  <si>
     <t>Setor não informado</t>
   </si>
   <si>
-    <t>Melhoria</t>
-  </si>
-  <si>
-    <t>Solicitação de serviço</t>
-  </si>
-  <si>
-    <t>Alteração em relatorio dentro do sistema "Apontamento de produção"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde, solicito a alteração no relatório de apontamento por funcionário quando "gerar o Excel". Preciso que no relatório saia o turno e o setor que cada funcionário faz parte ( inspeção END ou DIM). Motivo: Facilitar e otimizar o tempo de elaboração do relatório disponibilizado para liderança e </t>
-  </si>
-  <si>
-    <t>Média</t>
-  </si>
-  <si>
-    <t>Gerson Mendonça</t>
-  </si>
-  <si>
-    <t>Sistemas</t>
-  </si>
-  <si>
-    <t>18/05/2026</t>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Categoria não informada</t>
+  </si>
+  <si>
+    <t>Homologação IMPORTA_OS e EXPORTA_OS para a virada do MES</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Solicitante não informado</t>
+  </si>
+  <si>
+    <t>Equipe não informada</t>
+  </si>
+  <si>
+    <t>31/05/2026</t>
+  </si>
+  <si>
+    <t>36376</t>
+  </si>
+  <si>
+    <t>Engenharia</t>
+  </si>
+  <si>
+    <t>NOVA PERGUNTA ALERTA DE REVISÃO (copy)</t>
+  </si>
+  <si>
+    <t>Boa tarde, Favor incluir uma nova pergunta para todos os checklists de alerta de revisão. * A REVISÃO IMPACTA EM CUSTOS? Resposta "SIM" ou "NÃO". Caso a resposta seja "SIM" deve ser aberta uma segunda pergunta: * FOI SOLICITADA A REVISÃO DA FTF? Resposta "SIM" ou "NÃO". * A revisão só deve ser consi</t>
+  </si>
+  <si>
+    <t>Willian Gabriel Paixão dos Santos</t>
+  </si>
+  <si>
+    <t>05/05/2026</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
+  </si>
+  <si>
+    <t>12038376232</t>
+  </si>
+  <si>
+    <t>Layout ofertas exportação</t>
+  </si>
+  <si>
+    <t>17/05/2026</t>
+  </si>
+  <si>
+    <t>Impedimento</t>
+  </si>
+  <si>
+    <t>38407</t>
+  </si>
+  <si>
+    <t>Financeiro</t>
+  </si>
+  <si>
+    <t>Campo Forma de Liquidação - Cadastro de Fornecedor</t>
+  </si>
+  <si>
+    <t>Olá, Segue e-mail solicitação enviada referente as formas de pagamento. Atenciosamente, Atenção: Os pagamentos a Fornecedores da Electro Aço Altona S.A serão realizados/agendados todas as Segundas-feiras e Quintas-feiras. * Segunda-feira - paga-se os vencimentos de Segunda a Quarta-feira; * Quinta-f</t>
+  </si>
+  <si>
+    <t>Maria Andrade</t>
+  </si>
+  <si>
+    <t>ADH</t>
+  </si>
+  <si>
+    <t>15/05/2026</t>
+  </si>
+  <si>
+    <t>Feito</t>
+  </si>
+  <si>
+    <t>37298</t>
+  </si>
+  <si>
+    <t>Melhoria | Custo de venda Orçamento Nacional</t>
+  </si>
+  <si>
+    <t>Bom dia, Gentileza criar a melhoria na CPC impressa conforme abaixo: * Quando gerar uma CPC para cliente do mercado Nacional, apresentar os novos campos abaixo, abaixo do campo de frete: * % de despesa de frete, verificar com o comercial onde é preenchido (Aline) * %valor de despesa de frete orçado:</t>
+  </si>
+  <si>
+    <t>21/05/2026</t>
+  </si>
+  <si>
+    <t>38402</t>
+  </si>
+  <si>
+    <t>TELA DE IDENTIFICAÇÃO - CPP - Analise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia, Favor realizar as alterações para o processo de identificação para os sistemas PCP e CPP: 1. Nas telas NTCPP3 e WCPP221J criar um novo campo de "Identificação" contendo as seguintes informações: * Deve conter campos com um título denominado "Fixos CPP". A coluna da direita refere-se à tela </t>
+  </si>
+  <si>
+    <t>38027</t>
+  </si>
+  <si>
+    <t>Compras</t>
+  </si>
+  <si>
+    <t>Sistema manutenção</t>
+  </si>
+  <si>
+    <t>Bom dia, Colocar o a data da última saída do material no sistema de requisição da manutenção. Att</t>
+  </si>
+  <si>
+    <t>Alan Jonis da Silva</t>
+  </si>
+  <si>
+    <t>38029</t>
+  </si>
+  <si>
+    <t>Excelência Operacional</t>
+  </si>
+  <si>
+    <t>IROG - Tratamento Térmico</t>
+  </si>
+  <si>
+    <t>Bom dia Srs., Precisamos desenvolver uma performance encima do peso no tratamento térmico. Base de dados geradas pelo apontamento: Precisamos de uma tabela contendo "Peso Previsto" para cada carga do forno. O peso de cada carga seria a somatória do peso de todas as peças que foram tratadas nela. Exe</t>
+  </si>
+  <si>
+    <t>Gabriel Lucas Kertichka</t>
+  </si>
+  <si>
+    <t>38370</t>
+  </si>
+  <si>
+    <t>Controladoria</t>
+  </si>
+  <si>
+    <t>Relatório Modelos de Conjuntos e Componentes</t>
+  </si>
+  <si>
+    <t>Bom dia, a todos. @Sandro Schram, Gentileza desenvolver tela / relatório Excel com listagem de modelos de conjuntos e seus componentes, semelhante a planilha anexa. Posteriormente, essa implementação pode ser que interesse outras Equipes, e em outros demonstrativos como por exemplo Resumo de Carteir</t>
+  </si>
+  <si>
+    <t>Paulo Giovani da Cruz</t>
+  </si>
+  <si>
+    <t>37781</t>
+  </si>
+  <si>
+    <t>TI</t>
+  </si>
+  <si>
+    <t>Controle de sequência por nota fiscal -Trava no ROMANEIO</t>
+  </si>
+  <si>
+    <t>Prezados, Em reunião realizada nesta data, foram identificadas as demandas necessárias para a estruturação da DRE gerencial, com base nas notas fiscais emitidas no mês e no respectivo custo de cada sequência faturada, contemplando os grupos de receitas e despesas: - a linha de ROL, referente ao fatu</t>
+  </si>
+  <si>
+    <t>Edson João Hammermeister</t>
+  </si>
+  <si>
+    <t>37473</t>
+  </si>
+  <si>
+    <t>Bloqueio de apontamento eletrônico</t>
+  </si>
+  <si>
+    <t>Boa tarde senhores. Conforme discutido em reunião, abro este chamado para duas situações; 1. Setores a serem liberados a abrir apontamento eletrônico produtivo de sequencias que não tiveram a movimentação da fusão ou setores anteriores a fusão realizada. Corte: 1408/1411/1412/1413/1414/1415/1416/141</t>
+  </si>
+  <si>
+    <t>Bruno da Silva</t>
+  </si>
+  <si>
+    <t>38167</t>
+  </si>
+  <si>
+    <t>Problema</t>
+  </si>
+  <si>
+    <t>B.I. Acabamento - Jato Dirigido</t>
+  </si>
+  <si>
+    <t>Bom dia Srs., Encontramos mais inconsistências no B.I. do Acabamento! Avaliando os equipamentos Jato Dirigido 1º Lado e Jato Dirigido 2º Lado, identificamos que para um mesmo modelo e mesma operação, está puxando um Tempo Padrão diferente. Favor incluir uma coluna que demonstre o tempo padrão que fo</t>
+  </si>
+  <si>
+    <t>28/05/2026</t>
+  </si>
+  <si>
+    <t>37190</t>
+  </si>
+  <si>
+    <t>Mecânica</t>
+  </si>
+  <si>
+    <t>ALTERAÇÃO NO SISTEMA DE ORDENS.</t>
+  </si>
+  <si>
+    <t>Boa tarde, Gostaria de solicitar uma pequena alteração no sistema de Listas de ordens, onde para nós MANUTENÇÃO USINAGEM. Hoje aparece ordens de equipamentos pneumáticos, manutenção CIVIL, ENCANADOR, dentre outras que não fazem parte da nossa M.O, isso seria possível direcionar aos setores responsáv</t>
+  </si>
+  <si>
+    <t>Guilherme Ferreira</t>
+  </si>
+  <si>
+    <t>38315</t>
+  </si>
+  <si>
+    <t>WEB PDI AJUSTE CORRETIVO</t>
+  </si>
+  <si>
+    <t>Precisamos que tire a opção do inspetor de aprovar com desvio e refugar, isso é função apenas do analista. (urgente). Deixar apenas as opções abaixo e não cair para o analista avaliar quando o inspetor mandar para retrabalhar. att</t>
+  </si>
+  <si>
+    <t>12025088895</t>
+  </si>
+  <si>
+    <t>Atualizar status da OS no MES - Help chain</t>
+  </si>
+  <si>
+    <t>26/05/2026</t>
+  </si>
+  <si>
+    <t>12038553980</t>
+  </si>
+  <si>
+    <t>Levantamento de dados para Residencia de IA</t>
+  </si>
+  <si>
+    <t>38318</t>
+  </si>
+  <si>
+    <t>DPI eletronico ajuste corretivo</t>
+  </si>
+  <si>
+    <t>Gerar relatório para o cliente, alterável para o analista e fixo para controle interno att</t>
+  </si>
+  <si>
+    <t>37727</t>
+  </si>
+  <si>
+    <t>Contabilidade</t>
+  </si>
+  <si>
+    <t>Altona || Estoque de Imobilizado - Contabilização e Cálculo - Reunião</t>
+  </si>
+  <si>
+    <t>Bom dia, Sandro! Ainda temos pequenas diferenças na contabilização e cálculo do estoque de imobilizado. 1. NF 9630 Tecsensor – O SNB permitiu o crédito de PIS e Cofins. Acredito que tenha sido porque o CFOP estava 1.556. Diante disso, proponho o seguinte: a conta contábil será balizadora. Se a conta</t>
+  </si>
+  <si>
+    <t>Edson Vitor Scharf Filho</t>
+  </si>
+  <si>
+    <t>24/05/2026</t>
+  </si>
+  <si>
+    <t>12038554226</t>
+  </si>
+  <si>
+    <t>Sequencial number Clientes</t>
+  </si>
+  <si>
+    <t>38358</t>
+  </si>
+  <si>
+    <t>Melhorias Tratamento Térmico</t>
+  </si>
+  <si>
+    <t>Boa tarde, Com o funcionamento do piloto em um grupo de forno verificou que temos algumas melhorias , para facilitar o processo de cadastro de sequência, preparação e carregamento de cargas. * Para finalizar alguma parada o sistema solicita uma sequência, conseguimos tirar essa sequência; e também h</t>
+  </si>
+  <si>
+    <t>Eduardo Basso Pinto</t>
+  </si>
+  <si>
+    <t>38324</t>
+  </si>
+  <si>
+    <t>Web PDI corretivo/melhoria</t>
+  </si>
+  <si>
+    <t>Adicionar campo de observação de cada Sequência para o inspetor dar explicações sobre as peças para o analista. att</t>
+  </si>
+  <si>
+    <t>38351</t>
+  </si>
+  <si>
+    <t>Dashboard tabela Analise Geral de Manutenção</t>
+  </si>
+  <si>
+    <t>Bom dia, Solicito um chamado para desenvolvimento de um dashboard no QlikSense referente a planilha em Excel que está no link abaixo. Necessitamos que ela seja atualizada diariamente. As informações que buscamos para alimentar a planilha são diretamente da aplicação do Qlik: Manutenção -&gt; Controle d</t>
+  </si>
+  <si>
+    <t>Glória Danielly Lima Rodrigues</t>
+  </si>
+  <si>
+    <t>38248</t>
+  </si>
+  <si>
+    <t>Correção</t>
+  </si>
+  <si>
+    <t>ERRO: Entradas Sucata Retorno pelo Corte e Refugo - WEB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flávio boa tarde! Correções: Alguns casos de sequências que foram cortadas e não entraram no estoque de sucata retorno. Como exemplo: 572MU e 574MU Desconsiderar entrada em duplicidade: quando a Sequência que foi cortada posteriormente estornada (exclusão de movimentação) e movimentada novamente no </t>
+  </si>
+  <si>
+    <t>12038541393</t>
+  </si>
+  <si>
+    <t>IDENTIFICADOR ESPECIAL - LOT NUMBER</t>
+  </si>
+  <si>
+    <t>33130</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>Consulta Cadastro de LEADs</t>
   </si>
   <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Implantação</t>
-  </si>
-  <si>
-    <t>Não</t>
-  </si>
-  <si>
-    <t>Semana 3</t>
-  </si>
-  <si>
-    <t>Maio</t>
-  </si>
-  <si>
-    <t>37881</t>
-  </si>
-  <si>
-    <t>Almoxarifado</t>
-  </si>
-  <si>
-    <t>Automatização NF de transferência</t>
-  </si>
-  <si>
-    <t>Boa tarde! Atualmente, o processo de transferência de saldo (estoque atual e importação) é realizado de forma manual. A proposta é automatizar esse fluxo com base nas Notas Fiscais emitidas e recebidas. Hoje, o estoque de importação é controlado pela Total Comex. O objetivo é ativar uma flag por for</t>
-  </si>
-  <si>
-    <t>Alex Julio Estacio</t>
-  </si>
-  <si>
-    <t>30/04/2026</t>
-  </si>
-  <si>
-    <t>Fazendo</t>
-  </si>
-  <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>Semana 5</t>
-  </si>
-  <si>
-    <t>Abril</t>
-  </si>
-  <si>
-    <t>38071</t>
-  </si>
-  <si>
-    <t>Avaliação de Ferramenta - LogX Narwall - Reunião</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde, Estou abrindo o chamado para avaliação da integração com API aberta da Ferramental LogX da Narwal com o sistema de Invoice. Abaixo o link da documentação enviada pela empresa. Desconheço procedimentos, gentileza informar o que há necessidade do nosso lado para avaliação. Acredito que uma </t>
-  </si>
-  <si>
-    <t>Djalma Machado</t>
-  </si>
-  <si>
-    <t>A fazer</t>
-  </si>
-  <si>
-    <t>32079</t>
-  </si>
-  <si>
-    <t>TI</t>
-  </si>
-  <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>Homologação IMPORTA_OS e EXPORTA_OS para a virada do MES</t>
-  </si>
-  <si>
-    <t>Prezados, Precisamos validar a documentação enviada pela Directa, conforme reunião da ultima semana. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Edson João Hammermeister</t>
-  </si>
-  <si>
-    <t>36376</t>
-  </si>
-  <si>
-    <t>Categoria não informada</t>
-  </si>
-  <si>
-    <t>NOVA PERGUNTA ALERTA DE REVISÃO (copy)</t>
-  </si>
-  <si>
-    <t>Solicitante não informado</t>
-  </si>
-  <si>
-    <t>Equipe não informada</t>
-  </si>
-  <si>
-    <t>05/05/2026</t>
-  </si>
-  <si>
-    <t>Semana 1</t>
-  </si>
-  <si>
-    <t>37530</t>
-  </si>
-  <si>
-    <t>Layout ofertas exportação</t>
-  </si>
-  <si>
-    <t>Impedimento</t>
-  </si>
-  <si>
-    <t>38407</t>
-  </si>
-  <si>
-    <t>Campo Forma de Liquidação - Cadastro de Fornecedor</t>
-  </si>
-  <si>
-    <t>Olá, Segue e-mail solicitação enviada referente as formas de pagamento. Atenciosamente, Atenção: Os pagamentos a Fornecedores da Electro Aço Altona S.A serão realizados/agendados todas as Segundas-feiras e Quintas-feiras. * Segunda-feira - paga-se os vencimentos de Segunda a Quarta-feira; * Quinta-f</t>
-  </si>
-  <si>
-    <t>Maria Andrade</t>
-  </si>
-  <si>
-    <t>ADH</t>
-  </si>
-  <si>
-    <t>15/05/2026</t>
-  </si>
-  <si>
-    <t>Feito</t>
-  </si>
-  <si>
-    <t>37298</t>
-  </si>
-  <si>
-    <t>Melhoria | Custo de venda Orçamento Nacional</t>
-  </si>
-  <si>
-    <t>Bom dia, Gentileza criar a melhoria na CPC impressa conforme abaixo: * Quando gerar uma CPC para cliente do mercado Nacional, apresentar os novos campos abaixo, abaixo do campo de frete: * % de despesa de frete, verificar com o comercial onde é preenchido (Aline) * %valor de despesa de frete orçado:</t>
-  </si>
-  <si>
-    <t>38402</t>
-  </si>
-  <si>
-    <t>Engenharia</t>
-  </si>
-  <si>
-    <t>TELA DE IDENTIFICAÇÃO - CPP - Analise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia, Favor realizar as alterações para o processo de identificação para os sistemas PCP e CPP: 1. Nas telas NTCPP3 e WCPP221J criar um novo campo de "Identificação" contendo as seguintes informações: * Deve conter campos com um título denominado "Fixos CPP". A coluna da direita refere-se à tela </t>
-  </si>
-  <si>
-    <t>Willian Gabriel Paixão dos Santos</t>
-  </si>
-  <si>
-    <t>38027</t>
-  </si>
-  <si>
-    <t>Compras</t>
-  </si>
-  <si>
-    <t>Sistema manutenção</t>
-  </si>
-  <si>
-    <t>Bom dia, Colocar o a data da última saída do material no sistema de requisição da manutenção. Att</t>
-  </si>
-  <si>
-    <t>Alan Jonis da Silva</t>
-  </si>
-  <si>
-    <t>38029</t>
-  </si>
-  <si>
-    <t>Excelência Operacional</t>
-  </si>
-  <si>
-    <t>IROG - Tratamento Térmico</t>
-  </si>
-  <si>
-    <t>Bom dia Srs., Precisamos desenvolver uma performance encima do peso no tratamento térmico. Base de dados geradas pelo apontamento: Precisamos de uma tabela contendo "Peso Previsto" para cada carga do forno. O peso de cada carga seria a somatória do peso de todas as peças que foram tratadas nela. Exe</t>
-  </si>
-  <si>
-    <t>Gabriel Lucas Kertichka</t>
-  </si>
-  <si>
-    <t>38370</t>
-  </si>
-  <si>
-    <t>Relatório Modelos de Conjuntos e Componentes</t>
-  </si>
-  <si>
-    <t>Bom dia, a todos. @Sandro Schram, Gentileza desenvolver tela / relatório Excel com listagem de modelos de conjuntos e seus componentes, semelhante a planilha anexa. Posteriormente, essa implementação pode ser que interesse outras Equipes, e em outros demonstrativos como por exemplo Resumo de Carteir</t>
-  </si>
-  <si>
-    <t>Paulo Giovani da Cruz</t>
-  </si>
-  <si>
-    <t>37781</t>
-  </si>
-  <si>
-    <t>Controle de sequência por nota fiscal -Trava no ROMANEIO</t>
-  </si>
-  <si>
-    <t>Prezados, Em reunião realizada nesta data, foram identificadas as demandas necessárias para a estruturação da DRE gerencial, com base nas notas fiscais emitidas no mês e no respectivo custo de cada sequência faturada, contemplando os grupos de receitas e despesas: - a linha de ROL, referente ao fatu</t>
-  </si>
-  <si>
-    <t>37473</t>
-  </si>
-  <si>
-    <t>Bloqueio de apontamento eletrônico</t>
-  </si>
-  <si>
-    <t>Boa tarde senhores. Conforme discutido em reunião, abro este chamado para duas situações; 1. Setores a serem liberados a abrir apontamento eletrônico produtivo de sequencias que não tiveram a movimentação da fusão ou setores anteriores a fusão realizada. Corte: 1408/1411/1412/1413/1414/1415/1416/141</t>
-  </si>
-  <si>
-    <t>Bruno da Silva</t>
-  </si>
-  <si>
-    <t>38167</t>
-  </si>
-  <si>
-    <t>Problema</t>
-  </si>
-  <si>
-    <t>B.I. Acabamento - Jato Dirigido</t>
-  </si>
-  <si>
-    <t>Bom dia Srs., Encontramos mais inconsistências no B.I. do Acabamento! Avaliando os equipamentos Jato Dirigido 1º Lado e Jato Dirigido 2º Lado, identificamos que para um mesmo modelo e mesma operação, está puxando um Tempo Padrão diferente. Favor incluir uma coluna que demonstre o tempo padrão que fo</t>
-  </si>
-  <si>
-    <t>37190</t>
-  </si>
-  <si>
-    <t>ALTERAÇÃO NO SISTEMA DE ORDENS.</t>
-  </si>
-  <si>
-    <t>Boa tarde, Gostaria de solicitar uma pequena alteração no sistema de Listas de ordens, onde para nós MANUTENÇÃO USINAGEM. Hoje aparece ordens de equipamentos pneumáticos, manutenção CIVIL, ENCANADOR, dentre outras que não fazem parte da nossa M.O, isso seria possível direcionar aos setores responsáv</t>
-  </si>
-  <si>
-    <t>Guilherme Ferreira</t>
-  </si>
-  <si>
-    <t>38315</t>
-  </si>
-  <si>
-    <t>WEB PDI AJUSTE CORRETIVO</t>
-  </si>
-  <si>
-    <t>Precisamos que tire a opção do inspetor de aprovar com desvio e refugar, isso é função apenas do analista. (urgente). Deixar apenas as opções abaixo e não cair para o analista avaliar quando o inspetor mandar para retrabalhar. att</t>
-  </si>
-  <si>
-    <t>35890</t>
-  </si>
-  <si>
-    <t>Atualizar status da OS no MES - Help chain</t>
-  </si>
-  <si>
-    <t>31701</t>
-  </si>
-  <si>
-    <t>Levantamento de dados para Residencia de IA</t>
-  </si>
-  <si>
-    <t>38318</t>
-  </si>
-  <si>
-    <t>DPI eletronico ajuste corretivo</t>
-  </si>
-  <si>
-    <t>Gerar relatório para o cliente, alterável para o analista e fixo para controle interno att</t>
-  </si>
-  <si>
-    <t>37727</t>
-  </si>
-  <si>
-    <t>Altona || Estoque de Imobilizado - Contabilização e Cálculo - Reunião</t>
-  </si>
-  <si>
-    <t>Bom dia, Sandro! Ainda temos pequenas diferenças na contabilização e cálculo do estoque de imobilizado. 1. NF 9630 Tecsensor – O SNB permitiu o crédito de PIS e Cofins. Acredito que tenha sido porque o CFOP estava 1.556. Diante disso, proponho o seguinte: a conta contábil será balizadora. Se a conta</t>
-  </si>
-  <si>
-    <t>Edson Vitor Scharf Filho</t>
-  </si>
-  <si>
-    <t>36641</t>
-  </si>
-  <si>
-    <t>Sequencial number Clientes</t>
-  </si>
-  <si>
-    <t>38358</t>
-  </si>
-  <si>
-    <t>Melhorias Tratamento Térmico</t>
-  </si>
-  <si>
-    <t>Boa tarde, Com o funcionamento do piloto em um grupo de forno verificou que temos algumas melhorias , para facilitar o processo de cadastro de sequência, preparação e carregamento de cargas. * Para finalizar alguma parada o sistema solicita uma sequência, conseguimos tirar essa sequência; e também h</t>
-  </si>
-  <si>
-    <t>Eduardo Basso Pinto</t>
-  </si>
-  <si>
-    <t>38324</t>
-  </si>
-  <si>
-    <t>Web PDI corretivo/melhoria</t>
-  </si>
-  <si>
-    <t>Adicionar campo de observação de cada Sequência para o inspetor dar explicações sobre as peças para o analista. att</t>
-  </si>
-  <si>
-    <t>38351</t>
-  </si>
-  <si>
-    <t>Dashboard tabela Analise Geral de Manutenção</t>
-  </si>
-  <si>
-    <t>Bom dia, Solicito um chamado para desenvolvimento de um dashboard no QlikSense referente a planilha em Excel que está no link abaixo. Necessitamos que ela seja atualizada diariamente. As informações que buscamos para alimentar a planilha são diretamente da aplicação do Qlik: Manutenção -&gt; Controle d</t>
-  </si>
-  <si>
-    <t>Glória Danielly Lima Rodrigues</t>
-  </si>
-  <si>
-    <t>38248</t>
-  </si>
-  <si>
-    <t>Correção</t>
-  </si>
-  <si>
-    <t>ERRO: Entradas Sucata Retorno pelo Corte e Refugo - WEB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flávio boa tarde! Correções: Alguns casos de sequências que foram cortadas e não entraram no estoque de sucata retorno. Como exemplo: 572MU e 574MU Desconsiderar entrada em duplicidade: quando a Sequência que foi cortada posteriormente estornada (exclusão de movimentação) e movimentada novamente no </t>
-  </si>
-  <si>
-    <t>36055</t>
-  </si>
-  <si>
-    <t>IDENTIFICADOR ESPECIAL - LOT NUMBER</t>
-  </si>
-  <si>
-    <t>33130</t>
-  </si>
-  <si>
-    <t>Comercial</t>
-  </si>
-  <si>
-    <t>Consulta Cadastro de LEADs</t>
-  </si>
-  <si>
     <t>Laura Herrmann Schmickler</t>
   </si>
   <si>
@@ -459,6 +501,9 @@
     <t>Helena Mariana Segalla</t>
   </si>
   <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
     <t>37859</t>
   </si>
   <si>
@@ -474,6 +519,9 @@
     <t>37591</t>
   </si>
   <si>
+    <t>Manutenção</t>
+  </si>
+  <si>
     <t>Passar sistema de Ordens na TV e Gatilhos ACR para WEB</t>
   </si>
   <si>
@@ -495,7 +543,7 @@
     <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
   </si>
   <si>
-    <t>35448</t>
+    <t>11925878552</t>
   </si>
   <si>
     <t>Solicitação de melhoria no WMS – Pré-lista (EPI)</t>
@@ -564,7 +612,7 @@
     <t>Boa tarde, @Edson João Hammermeister conforme conversamos na reunião, favor seguir com a integração da máquina Cenci, acredito que já esteva conversando com eles. https://documenter.getpostman.com/view/24484248/2sA3kRJPEZ#282fad9d-f4d0-48ff-b7c0-62f4e8fe2ba5 Fico no aguardo do retorno. Att</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>12038502606</t>
   </si>
   <si>
     <t>Novo Sistema</t>
@@ -573,12 +621,12 @@
     <t>Verificar se foi vinculada a entrada e saida com o outro módulo do sistema - Analise</t>
   </si>
   <si>
+    <t>12049786981</t>
+  </si>
+  <si>
     <t>Verificar se foi vinculada a entrada e saida com o outro módulo do sistema - Implantação</t>
   </si>
   <si>
-    <t>19/05/2026</t>
-  </si>
-  <si>
     <t>Atualizar campos: data, hora e prazo da proposta</t>
   </si>
   <si>
@@ -609,6 +657,9 @@
     <t>38507</t>
   </si>
   <si>
+    <t>Usinagem</t>
+  </si>
+  <si>
     <t>Alteração de aplicação</t>
   </si>
   <si>
@@ -621,7 +672,7 @@
     <t>Controle de sequência por nota fiscal - Alerta notas fiscais sem sequencia informada (copy)</t>
   </si>
   <si>
-    <t>35602</t>
+    <t>11989074264</t>
   </si>
   <si>
     <t>Gerenciamento de Sessão de Leitura (Draft State)</t>
@@ -630,6 +681,9 @@
     <t>12/05/2026</t>
   </si>
   <si>
+    <t>20/05/2026</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
@@ -681,6 +735,12 @@
     <t>[COMPRAS] MELHORIA NF de devolução e baixa de estoque</t>
   </si>
   <si>
+    <t>Bom dia Prezados Espero que estejam bem. Precisamos da implementação de uma funcionalidade no que diz respeito a NF de devolução e baixa de estoque: CENÁRIO ATUAL A NF de devolução é emitida e saldo do item continua no sistema, requerendo que a baixa seja efetuada manualmente. O que, por vezes, ocas</t>
+  </si>
+  <si>
+    <t>Alini Ferreira Ganda</t>
+  </si>
+  <si>
     <t>38369</t>
   </si>
   <si>
@@ -696,7 +756,7 @@
     <t>Calculo do custo - Inspeção - subáreas</t>
   </si>
   <si>
-    <t>36724</t>
+    <t>12038507672</t>
   </si>
   <si>
     <t>Alteração de registro de pintura</t>
@@ -726,7 +786,7 @@
     <t>Bloqueio de apontamento eletrônico - Acompanhamento</t>
   </si>
   <si>
-    <t>34073</t>
+    <t>11960334805</t>
   </si>
   <si>
     <t>Callback em aplicações WEB</t>
@@ -744,7 +804,7 @@
     <t>Bom dia, Favor incluir uma coluna com a data de envio da pendencia ao compras na tela principal de pendencias, conforme abaixo em amarelo. http://1.0.2.131/programasweb/wpendencianfe.aspx Att</t>
   </si>
   <si>
-    <t>32073</t>
+    <t>12038294308</t>
   </si>
   <si>
     <t>Listar sequencias com status de encerrado na usinagem</t>
@@ -762,6 +822,9 @@
     <t>Fernando Beltrame</t>
   </si>
   <si>
+    <t>11989088474</t>
+  </si>
+  <si>
     <t>Testes de funcionalidade e refino visual</t>
   </si>
   <si>
@@ -786,6 +849,9 @@
     <t>Preciso que seja arrumado a forma que o relatório de PDI eletrônico seja impresso. Hoje o relatório aparece dessa forma, e não é apenas em um pdi, é em diversos</t>
   </si>
   <si>
+    <t>11989101922</t>
+  </si>
+  <si>
     <t>Adaptação do Web Panel para Múltiplas Peças</t>
   </si>
   <si>
@@ -807,9 +873,6 @@
     <t>37963</t>
   </si>
   <si>
-    <t>Logística</t>
-  </si>
-  <si>
     <t>Chamado Caminhão Munck - WMS</t>
   </si>
   <si>
@@ -846,7 +909,7 @@
     <t xml:space="preserve">Bom dia, Conforme conversamos, segue solicitado para criar base histórica do reconhecimento de receita. Necessário gerar congelamento no último dia do mês e todo domingo (semanal). Segundo Alexandro, a necessidade é de 1 mês e meio de histórico. Regras na Tabela * Coluna - reconhecimento de receita </t>
   </si>
   <si>
-    <t>36046</t>
+    <t>12038375899</t>
   </si>
   <si>
     <t>Aprimoramento Ailton - Acompanhamento</t>
@@ -855,6 +918,9 @@
     <t>30012</t>
   </si>
   <si>
+    <t>PCP</t>
+  </si>
+  <si>
     <t>Painel OP - Acompanhamento</t>
   </si>
   <si>
@@ -864,226 +930,223 @@
     <t>João Pedro Beccon</t>
   </si>
   <si>
+    <t>Bloqueio de apontamento eletrônico - Envio de e-mail (copy)</t>
+  </si>
+  <si>
+    <t>36722</t>
+  </si>
+  <si>
+    <t>Bloco K - Integração dados Altona / Benner.</t>
+  </si>
+  <si>
+    <t>Prezado, bom dia. Situação: Atualmente a integração dos dados Altona / Benner, para integrar o bloco K, precisa da intervenção de uma pessoa para disparar a rotina. Necessidade: Automatizar este processo. Ação: 1. Implementar status indicando que o dado está pronto para ser enviado para Benner. 2. A</t>
+  </si>
+  <si>
+    <t>36335</t>
+  </si>
+  <si>
+    <t>Ajuste em gráficos no B.I - Alteração Dashboard</t>
+  </si>
+  <si>
+    <t>Boa tarde, Preciso de uns ajustes no Qlik Sense, existe um gráfico que fala sobre a movimentação da moldagem USE (Segue imagem do local): Essa é Tela inicial: 1 - Olhando para a questão dos filtros, preciso de uma filtro para semana, exemplo semana 2 (04/01 até 10/01), assim consigo visualizar melho</t>
+  </si>
+  <si>
+    <t>Matheus Rodrigues de Almeida</t>
+  </si>
+  <si>
+    <t>25/05/2026</t>
+  </si>
+  <si>
+    <t>Ajuste em gráficos no B.I - Extração e consultas</t>
+  </si>
+  <si>
+    <t>Calculo do custo - Apoio - subáreas (copy)</t>
+  </si>
+  <si>
+    <t>12044640432</t>
+  </si>
+  <si>
+    <t>Atualização de versão</t>
+  </si>
+  <si>
+    <t>Enviar KBs para server</t>
+  </si>
+  <si>
+    <t>35527</t>
+  </si>
+  <si>
+    <t>Orçamento 2025</t>
+  </si>
+  <si>
+    <t>Boa tarde, Segue a planilha com a estrutura de orçamento, conforme alinhado na reunião. Atenciosamente,</t>
+  </si>
+  <si>
+    <t>Marcio Silva</t>
+  </si>
+  <si>
+    <t>06/04/2026</t>
+  </si>
+  <si>
+    <t>37499</t>
+  </si>
+  <si>
+    <t>Alteração sistema registro USE-ULE Windows</t>
+  </si>
+  <si>
+    <t>Bom dia, Necessitamos que seja feita uma alteração no sistema de registro USE-ULE, precisamos que as imagens que ficam anexas as perguntas, quando exibidas pelo relatório do botão "Imprime Registro" sejam de um tamanho maior, que seja possível analisar de forma clara pelo computador. Sugerimos que s</t>
+  </si>
+  <si>
+    <t>João Eduardo Zarth</t>
+  </si>
+  <si>
+    <t>17/04/2026</t>
+  </si>
+  <si>
+    <t>37468</t>
+  </si>
+  <si>
+    <t>SETOR 7013</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor criar sistemática em roteiro e fluxo de produção para que quando setor 7013 for utilizado faça a movimentação automática e envie e-mail padrão conforme abaixo: "A sequência XXXXX foi movimentada do setor 7013, portanto reter a documentação necessária para o databook". O "XXXXX" deve v</t>
+  </si>
+  <si>
+    <t>37790</t>
+  </si>
+  <si>
+    <t>Melhoria chamado 36299</t>
+  </si>
+  <si>
+    <t>Bom dia, Solicito um chamado para uma analise para os dados que estão sendo puxados do tempo produtivo da máquina em relação ao MTBF, o ideal seria puxar o planejado/esperado da máquina pois durante o dia ocorre "ns" situações de parada além das manutenções e isso afeta nosso mtbf e disponibilidade.</t>
+  </si>
+  <si>
+    <t>38205</t>
+  </si>
+  <si>
+    <t>Melhoria sistema de apontamento fornos de Tratamento Térmico</t>
+  </si>
+  <si>
+    <t>Bom dia, Precisamos de algumas melhorias no sistema. * Ao finalizar a carga separar a etapa de resfriamento e do descarregamento, muitas vezes a carga sai e não é o mesmo turno que descarrega. * Adicionar a pré-lista a mensagem de que a sequência não está no setor do tratamento térmico, informando e</t>
+  </si>
+  <si>
+    <t>38231</t>
+  </si>
+  <si>
+    <t>Melhoria sistema ToTo</t>
+  </si>
+  <si>
+    <t>Bom dia, Para melhorar a utilização do sistema dos fornos, precisamos fazer algumas melhorias no sistema. * Seria possível fazer uma linha do tempo de paradas apontadas nesse campo abaixo da programação, exemplo lista o forno, a carga sempre a que finalizou, e as paradas, pontadas até o início da pr</t>
+  </si>
+  <si>
+    <t>38516</t>
+  </si>
+  <si>
+    <t>Ajuste tela proformas</t>
+  </si>
+  <si>
+    <t>Boa tarde Maciel, Poderia avaliar a possibilidade de incluir a informação de "numero da proforma" nessa tela, facilitaria a nossa consulta e troca de informações com o financeiro. Obrigada!</t>
+  </si>
+  <si>
+    <t>Luciane Krindges</t>
+  </si>
+  <si>
+    <t>12062254140</t>
+  </si>
+  <si>
+    <t>ALTC - F3</t>
+  </si>
+  <si>
+    <t>37483</t>
+  </si>
+  <si>
+    <t>Falta Apontamentos de Setup - aplicação Usinagem IROG</t>
+  </si>
+  <si>
+    <t>Olá, Favor verificar o motivo da falta dos apontamentos de Setup na aplicação Usinagem IROG, segue exemplo: Entre o período assinalado existe um apontamento de Setup, o qual não está aparecendo na aplicação. Grato,</t>
+  </si>
+  <si>
+    <t>Caio Henrique Vicente Bento</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
+  </si>
+  <si>
+    <t>APS-unificação dos modelos genexus</t>
+  </si>
+  <si>
+    <t>29/05/2026</t>
+  </si>
+  <si>
+    <t>APS-Geração de dados ERP x APS automatica</t>
+  </si>
+  <si>
+    <t>APS-Upload planilha modelos de terceiros</t>
+  </si>
+  <si>
+    <t>APS-Geração das operações nos modelos com terceiros</t>
+  </si>
+  <si>
+    <t>APS-Geração grupo de recursos fornos ToTo</t>
+  </si>
+  <si>
+    <t>Dashboard de Change Log - Governança de TI</t>
+  </si>
+  <si>
+    <t>Período</t>
+  </si>
+  <si>
+    <t>Mar/2026</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Tickets corporativos para intranet / Power BI / Excel</t>
+  </si>
+  <si>
+    <t>Total de tickets</t>
+  </si>
+  <si>
+    <t>% dentro do SLA</t>
+  </si>
+  <si>
+    <t>Tempo médio (dias)</t>
+  </si>
+  <si>
+    <t>Áreas atendidas</t>
+  </si>
+  <si>
+    <t>Status final</t>
+  </si>
+  <si>
+    <t>Encerrado</t>
+  </si>
+  <si>
+    <t>Resumo Executivo</t>
+  </si>
+  <si>
+    <t>Tickets por Área</t>
+  </si>
+  <si>
+    <t>Distribuição por Tipo</t>
+  </si>
+  <si>
+    <t>Cumprimento SLA (15 dias)</t>
+  </si>
+  <si>
+    <t>Status Final</t>
+  </si>
+  <si>
+    <t>Tickets por Semana</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>Muito Alta</t>
+  </si>
+  <si>
     <t>Sim</t>
-  </si>
-  <si>
-    <t>Bloqueio de apontamento eletrônico - Envio de e-mail (copy)</t>
-  </si>
-  <si>
-    <t>36722</t>
-  </si>
-  <si>
-    <t>Bloco K - Integração dados Altona / Benner.</t>
-  </si>
-  <si>
-    <t>36335</t>
-  </si>
-  <si>
-    <t>Fundição</t>
-  </si>
-  <si>
-    <t>Ajuste em gráficos no B.I - Alteração Dashboard</t>
-  </si>
-  <si>
-    <t>Boa tarde, Preciso de uns ajustes no Qlik Sense, existe um gráfico que fala sobre a movimentação da moldagem USE (Segue imagem do local): Essa é Tela inicial: 1 - Olhando para a questão dos filtros, preciso de uma filtro para semana, exemplo semana 2 (04/01 até 10/01), assim consigo visualizar melho</t>
-  </si>
-  <si>
-    <t>Matheus Rodrigues de Almeida</t>
-  </si>
-  <si>
-    <t>Ajuste em gráficos no B.I - Extração e consultas</t>
-  </si>
-  <si>
-    <t>31/05/2026</t>
-  </si>
-  <si>
-    <t>Calculo do custo - Apoio - subáreas (copy)</t>
-  </si>
-  <si>
-    <t>Atualização de versão</t>
-  </si>
-  <si>
-    <t>Enviar KBs para server</t>
-  </si>
-  <si>
-    <t>35527</t>
-  </si>
-  <si>
-    <t>Orçamento 2025</t>
-  </si>
-  <si>
-    <t>Boa tarde, Segue a planilha com a estrutura de orçamento, conforme alinhado na reunião. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Marcio Silva</t>
-  </si>
-  <si>
-    <t>06/04/2026</t>
-  </si>
-  <si>
-    <t>37499</t>
-  </si>
-  <si>
-    <t>Alteração sistema registro USE-ULE Windows</t>
-  </si>
-  <si>
-    <t>Bom dia, Necessitamos que seja feita uma alteração no sistema de registro USE-ULE, precisamos que as imagens que ficam anexas as perguntas, quando exibidas pelo relatório do botão "Imprime Registro" sejam de um tamanho maior, que seja possível analisar de forma clara pelo computador. Sugerimos que s</t>
-  </si>
-  <si>
-    <t>João Eduardo Zarth</t>
-  </si>
-  <si>
-    <t>17/04/2026</t>
-  </si>
-  <si>
-    <t>37468</t>
-  </si>
-  <si>
-    <t>SETOR 7013</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor criar sistemática em roteiro e fluxo de produção para que quando setor 7013 for utilizado faça a movimentação automática e envie e-mail padrão conforme abaixo: "A sequência XXXXX foi movimentada do setor 7013, portanto reter a documentação necessária para o databook". O "XXXXX" deve v</t>
-  </si>
-  <si>
-    <t>37790</t>
-  </si>
-  <si>
-    <t>Melhoria chamado 36299</t>
-  </si>
-  <si>
-    <t>Bom dia, Solicito um chamado para uma analise para os dados que estão sendo puxados do tempo produtivo da máquina em relação ao MTBF, o ideal seria puxar o planejado/esperado da máquina pois durante o dia ocorre "ns" situações de parada além das manutenções e isso afeta nosso mtbf e disponibilidade.</t>
-  </si>
-  <si>
-    <t>38205</t>
-  </si>
-  <si>
-    <t>Melhoria sistema de apontamento fornos de Tratamento Térmico</t>
-  </si>
-  <si>
-    <t>Bom dia, Precisamos de algumas melhorias no sistema. * Ao finalizar a carga separar a etapa de resfriamento e do descarregamento, muitas vezes a carga sai e não é o mesmo turno que descarrega. * Adicionar a pré-lista a mensagem de que a sequência não está no setor do tratamento térmico, informando e</t>
-  </si>
-  <si>
-    <t>20/05/2026</t>
-  </si>
-  <si>
-    <t>38231</t>
-  </si>
-  <si>
-    <t>Melhoria sistema ToTo</t>
-  </si>
-  <si>
-    <t>Bom dia, Para melhorar a utilização do sistema dos fornos, precisamos fazer algumas melhorias no sistema. * Seria possível fazer uma linha do tempo de paradas apontadas nesse campo abaixo da programação, exemplo lista o forno, a carga sempre a que finalizou, e as paradas, pontadas até o início da pr</t>
-  </si>
-  <si>
-    <t>38516</t>
-  </si>
-  <si>
-    <t>Ajuste tela proformas</t>
-  </si>
-  <si>
-    <t>Boa tarde Maciel, Poderia avaliar a possibilidade de incluir a informação de "numero da proforma" nessa tela, facilitaria a nossa consulta e troca de informações com o financeiro. Obrigada!</t>
-  </si>
-  <si>
-    <t>Luciane Krindges</t>
-  </si>
-  <si>
-    <t>ALTC - F3</t>
-  </si>
-  <si>
-    <t>37483</t>
-  </si>
-  <si>
-    <t>Usinagem</t>
-  </si>
-  <si>
-    <t>Falta Apontamentos de Setup - aplicação Usinagem IROG</t>
-  </si>
-  <si>
-    <t>Olá, Favor verificar o motivo da falta dos apontamentos de Setup na aplicação Usinagem IROG, segue exemplo: Entre o período assinalado existe um apontamento de Setup, o qual não está aparecendo na aplicação. Grato,</t>
-  </si>
-  <si>
-    <t>Caio Henrique Vicente Bento</t>
-  </si>
-  <si>
-    <t>26/05/2026</t>
-  </si>
-  <si>
-    <t>Semana 4</t>
-  </si>
-  <si>
-    <t>APS-unificação dos modelos genexus</t>
-  </si>
-  <si>
-    <t>29/05/2026</t>
-  </si>
-  <si>
-    <t>APS-Geração de dados ERP x APS automatica</t>
-  </si>
-  <si>
-    <t>APS-Upload planilha modelos de terceiros</t>
-  </si>
-  <si>
-    <t>APS-Geração das operações nos modelos com terceiros</t>
-  </si>
-  <si>
-    <t>APS-Geração grupo de recursos fornos ToTo</t>
-  </si>
-  <si>
-    <t>Dashboard de Change Log - Governança de TI</t>
-  </si>
-  <si>
-    <t>Período</t>
-  </si>
-  <si>
-    <t>SPRINT 2026-14</t>
-  </si>
-  <si>
-    <t>Base</t>
-  </si>
-  <si>
-    <t>Tickets corporativos para intranet / Power BI / Excel</t>
-  </si>
-  <si>
-    <t>Total de tickets</t>
-  </si>
-  <si>
-    <t>% dentro do SLA</t>
-  </si>
-  <si>
-    <t>Tempo médio (dias)</t>
-  </si>
-  <si>
-    <t>Áreas atendidas</t>
-  </si>
-  <si>
-    <t>Status final</t>
-  </si>
-  <si>
-    <t>Encerrado</t>
-  </si>
-  <si>
-    <t>Resumo Executivo</t>
-  </si>
-  <si>
-    <t>Tickets por Área</t>
-  </si>
-  <si>
-    <t>Distribuição por Tipo</t>
-  </si>
-  <si>
-    <t>Cumprimento SLA (15 dias)</t>
-  </si>
-  <si>
-    <t>Status Final</t>
-  </si>
-  <si>
-    <t>Tickets por Semana</t>
-  </si>
-  <si>
-    <t>Volume</t>
-  </si>
-  <si>
-    <t>Muito Alta</t>
   </si>
   <si>
     <t>Abertos</t>
@@ -1662,13 +1725,13 @@
         <v>35</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>38</v>
@@ -1682,7 +1745,7 @@
         <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>
@@ -1691,16 +1754,16 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>23</v>
@@ -1709,13 +1772,13 @@
         <v>24</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>28</v>
@@ -1726,37 +1789,37 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>26</v>
@@ -1773,34 +1836,34 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>25</v>
@@ -1812,7 +1875,7 @@
         <v>27</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>29</v>
@@ -1820,43 +1883,43 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>28</v>
@@ -1867,10 +1930,10 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>17</v>
@@ -1879,28 +1942,28 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>27</v>
@@ -1914,10 +1977,10 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>17</v>
@@ -1926,16 +1989,16 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>23</v>
@@ -1944,7 +2007,7 @@
         <v>24</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>26</v>
@@ -1961,10 +2024,10 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>17</v>
@@ -1973,28 +2036,28 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>27</v>
@@ -2008,10 +2071,10 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>17</v>
@@ -2020,16 +2083,16 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>23</v>
@@ -2041,7 +2104,7 @@
         <v>25</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>27</v>
@@ -2055,10 +2118,10 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>17</v>
@@ -2067,16 +2130,16 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>23</v>
@@ -2085,13 +2148,13 @@
         <v>35</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>38</v>
@@ -2102,10 +2165,10 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>17</v>
@@ -2114,28 +2177,28 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>27</v>
@@ -2149,10 +2212,10 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>17</v>
@@ -2161,16 +2224,16 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>23</v>
@@ -2179,10 +2242,10 @@
         <v>24</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>27</v>
@@ -2196,7 +2259,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -2208,16 +2271,16 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>23</v>
@@ -2226,13 +2289,13 @@
         <v>24</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>28</v>
@@ -2243,28 +2306,28 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>23</v>
@@ -2273,10 +2336,10 @@
         <v>35</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>27</v>
@@ -2290,10 +2353,10 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>17</v>
@@ -2302,16 +2365,16 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>23</v>
@@ -2323,7 +2386,7 @@
         <v>25</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>27</v>
@@ -2337,7 +2400,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -2349,10 +2412,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>21</v>
@@ -2364,13 +2427,13 @@
         <v>23</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>27</v>
@@ -2384,43 +2447,43 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="I19" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>25</v>
+        <v>121</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>28</v>
@@ -2431,40 +2494,40 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>27</v>
@@ -2478,7 +2541,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -2490,10 +2553,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>21</v>
@@ -2505,16 +2568,16 @@
         <v>23</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>28</v>
@@ -2525,10 +2588,10 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>17</v>
@@ -2537,28 +2600,28 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>25</v>
+        <v>132</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>27</v>
@@ -2572,43 +2635,43 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="I23" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>28</v>
@@ -2619,7 +2682,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2631,28 +2694,28 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>27</v>
@@ -2666,7 +2729,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2678,10 +2741,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>21</v>
@@ -2693,13 +2756,13 @@
         <v>23</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>27</v>
@@ -2713,10 +2776,10 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>17</v>
@@ -2725,31 +2788,31 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>28</v>
@@ -2760,34 +2823,34 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>25</v>
@@ -2807,43 +2870,43 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="I28" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>28</v>
@@ -2854,28 +2917,28 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>25</v>
+        <v>155</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>23</v>
@@ -2884,13 +2947,13 @@
         <v>24</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>28</v>
@@ -2901,10 +2964,10 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>17</v>
@@ -2913,16 +2976,16 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>23</v>
@@ -2931,10 +2994,10 @@
         <v>24</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>25</v>
+        <v>162</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>27</v>
@@ -2948,10 +3011,10 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>17</v>
@@ -2960,16 +3023,16 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>23</v>
@@ -2978,13 +3041,13 @@
         <v>35</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>38</v>
@@ -2995,10 +3058,10 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>17</v>
@@ -3007,16 +3070,16 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>23</v>
@@ -3025,10 +3088,10 @@
         <v>24</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>25</v>
+        <v>162</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>27</v>
@@ -3042,46 +3105,46 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="M33" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>29</v>
@@ -3089,43 +3152,43 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>28</v>
@@ -3136,46 +3199,46 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D35" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="I35" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>29</v>
@@ -3183,10 +3246,10 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>17</v>
@@ -3195,16 +3258,16 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>23</v>
@@ -3213,13 +3276,13 @@
         <v>24</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>28</v>
@@ -3230,10 +3293,10 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>17</v>
@@ -3242,16 +3305,16 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>23</v>
@@ -3263,7 +3326,7 @@
         <v>25</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M37" s="2" t="s">
         <v>27</v>
@@ -3277,10 +3340,10 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>17</v>
@@ -3289,16 +3352,16 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>23</v>
@@ -3307,10 +3370,10 @@
         <v>35</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>27</v>
@@ -3324,10 +3387,10 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>17</v>
@@ -3336,16 +3399,16 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>23</v>
@@ -3354,13 +3417,13 @@
         <v>24</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>28</v>
@@ -3371,10 +3434,10 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>17</v>
@@ -3383,16 +3446,16 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>23</v>
@@ -3401,13 +3464,13 @@
         <v>24</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>25</v>
+        <v>121</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>28</v>
@@ -3418,10 +3481,10 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>17</v>
@@ -3430,34 +3493,34 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>29</v>
@@ -3465,40 +3528,40 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="D42" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H42" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="I42" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>27</v>
@@ -3512,40 +3575,40 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H43" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="I43" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M43" s="2" t="s">
         <v>27</v>
@@ -3559,28 +3622,28 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>25</v>
+        <v>155</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>23</v>
@@ -3589,13 +3652,13 @@
         <v>24</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>25</v>
+        <v>162</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>28</v>
@@ -3606,10 +3669,10 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>17</v>
@@ -3618,28 +3681,28 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>25</v>
+        <v>121</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M45" s="2" t="s">
         <v>27</v>
@@ -3653,10 +3716,10 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>17</v>
@@ -3665,28 +3728,28 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M46" s="2" t="s">
         <v>27</v>
@@ -3700,10 +3763,10 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>16</v>
+        <v>214</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>17</v>
@@ -3712,28 +3775,28 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M47" s="2" t="s">
         <v>27</v>
@@ -3747,10 +3810,10 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>17</v>
@@ -3759,16 +3822,16 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>23</v>
@@ -3777,10 +3840,10 @@
         <v>24</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M48" s="2" t="s">
         <v>27</v>
@@ -3794,46 +3857,46 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D49" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H49" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="I49" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>25</v>
+        <v>222</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M49" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>29</v>
@@ -3841,28 +3904,28 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>23</v>
@@ -3874,7 +3937,7 @@
         <v>25</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M50" s="2" t="s">
         <v>27</v>
@@ -3888,10 +3951,10 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>17</v>
@@ -3900,16 +3963,16 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>23</v>
@@ -3918,10 +3981,10 @@
         <v>24</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>25</v>
+        <v>222</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M51" s="2" t="s">
         <v>27</v>
@@ -3935,7 +3998,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
@@ -3947,16 +4010,16 @@
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>23</v>
@@ -3965,13 +4028,13 @@
         <v>24</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>25</v>
+        <v>162</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>28</v>
@@ -3982,10 +4045,10 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>17</v>
@@ -3994,22 +4057,22 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>25</v>
@@ -4021,7 +4084,7 @@
         <v>27</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="O53" s="2" t="s">
         <v>29</v>
@@ -4029,10 +4092,10 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>17</v>
@@ -4041,16 +4104,16 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>23</v>
@@ -4059,10 +4122,10 @@
         <v>35</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M54" s="2" t="s">
         <v>27</v>
@@ -4076,10 +4139,10 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>17</v>
@@ -4088,16 +4151,16 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>23</v>
@@ -4106,10 +4169,10 @@
         <v>24</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M55" s="2" t="s">
         <v>27</v>
@@ -4123,43 +4186,43 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>55</v>
+        <v>241</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N56" s="2" t="s">
         <v>28</v>
@@ -4170,10 +4233,10 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>17</v>
@@ -4182,28 +4245,28 @@
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M57" s="2" t="s">
         <v>27</v>
@@ -4217,10 +4280,10 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>17</v>
@@ -4229,16 +4292,16 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>23</v>
@@ -4247,13 +4310,13 @@
         <v>24</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>28</v>
@@ -4264,43 +4327,43 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>28</v>
@@ -4311,7 +4374,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
@@ -4323,28 +4386,28 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M60" s="2" t="s">
         <v>27</v>
@@ -4358,10 +4421,10 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>17</v>
@@ -4370,16 +4433,16 @@
         <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>23</v>
@@ -4391,7 +4454,7 @@
         <v>25</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M61" s="2" t="s">
         <v>27</v>
@@ -4405,7 +4468,7 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
@@ -4417,16 +4480,16 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>23</v>
@@ -4435,10 +4498,10 @@
         <v>24</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>27</v>
@@ -4452,46 +4515,46 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D63" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H63" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="I63" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>29</v>
@@ -4499,10 +4562,10 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>17</v>
@@ -4511,28 +4574,28 @@
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M64" s="2" t="s">
         <v>27</v>
@@ -4546,40 +4609,40 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D65" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H65" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="I65" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M65" s="2" t="s">
         <v>27</v>
@@ -4593,7 +4656,7 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>16</v>
@@ -4605,16 +4668,16 @@
         <v>18</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>23</v>
@@ -4640,46 +4703,46 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>202</v>
+        <v>269</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D67" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H67" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="I67" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>25</v>
+        <v>222</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M67" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="O67" s="2" t="s">
         <v>29</v>
@@ -4687,7 +4750,7 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>16</v>
@@ -4699,16 +4762,16 @@
         <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>23</v>
@@ -4734,7 +4797,7 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>16</v>
@@ -4746,10 +4809,10 @@
         <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>21</v>
@@ -4761,13 +4824,13 @@
         <v>23</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M69" s="2" t="s">
         <v>27</v>
@@ -4781,46 +4844,46 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>202</v>
+        <v>278</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D70" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H70" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="I70" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>25</v>
+        <v>222</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M70" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="O70" s="2" t="s">
         <v>29</v>
@@ -4828,7 +4891,7 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>31</v>
@@ -4840,10 +4903,10 @@
         <v>18</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>21</v>
@@ -4855,13 +4918,13 @@
         <v>23</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M71" s="2" t="s">
         <v>27</v>
@@ -4875,7 +4938,7 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>16</v>
@@ -4887,10 +4950,10 @@
         <v>18</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>21</v>
@@ -4902,13 +4965,13 @@
         <v>23</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M72" s="2" t="s">
         <v>27</v>
@@ -4922,10 +4985,10 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>264</v>
+        <v>41</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>17</v>
@@ -4934,16 +4997,16 @@
         <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>23</v>
@@ -4969,10 +5032,10 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>17</v>
@@ -4981,28 +5044,28 @@
         <v>18</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M74" s="2" t="s">
         <v>27</v>
@@ -5011,15 +5074,15 @@
         <v>28</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>17</v>
@@ -5028,16 +5091,16 @@
         <v>18</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>23</v>
@@ -5046,13 +5109,13 @@
         <v>24</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N75" s="2" t="s">
         <v>28</v>
@@ -5063,40 +5126,40 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>25</v>
+        <v>132</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M76" s="2" t="s">
         <v>27</v>
@@ -5110,28 +5173,28 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>16</v>
+        <v>301</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>23</v>
@@ -5140,13 +5203,13 @@
         <v>24</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>283</v>
+        <v>27</v>
       </c>
       <c r="N77" s="2" t="s">
         <v>28</v>
@@ -5157,7 +5220,7 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>16</v>
@@ -5169,16 +5232,16 @@
         <v>18</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>23</v>
@@ -5187,13 +5250,13 @@
         <v>24</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N78" s="2" t="s">
         <v>28</v>
@@ -5204,31 +5267,31 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>55</v>
+        <v>192</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>24</v>
@@ -5237,7 +5300,7 @@
         <v>25</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M79" s="2" t="s">
         <v>27</v>
@@ -5251,10 +5314,10 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>288</v>
+        <v>16</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>17</v>
@@ -5263,16 +5326,16 @@
         <v>18</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>23</v>
@@ -5281,10 +5344,10 @@
         <v>24</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>25</v>
+        <v>313</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>27</v>
@@ -5298,10 +5361,10 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>288</v>
+        <v>16</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>17</v>
@@ -5310,28 +5373,28 @@
         <v>18</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>293</v>
+        <v>55</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>25</v>
+        <v>313</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M81" s="2" t="s">
         <v>27</v>
@@ -5345,10 +5408,10 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>17</v>
@@ -5357,16 +5420,16 @@
         <v>18</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>23</v>
@@ -5375,13 +5438,13 @@
         <v>24</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N82" s="2" t="s">
         <v>28</v>
@@ -5392,43 +5455,43 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>237</v>
+        <v>316</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N83" s="2" t="s">
         <v>28</v>
@@ -5439,10 +5502,10 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>17</v>
@@ -5451,34 +5514,34 @@
         <v>18</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="O84" s="2" t="s">
         <v>39</v>
@@ -5486,7 +5549,7 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>16</v>
@@ -5498,28 +5561,28 @@
         <v>18</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M85" s="2" t="s">
         <v>27</v>
@@ -5533,10 +5596,10 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>17</v>
@@ -5545,28 +5608,28 @@
         <v>18</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="K86" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M86" s="2" t="s">
         <v>27</v>
@@ -5580,10 +5643,10 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>17</v>
@@ -5592,31 +5655,31 @@
         <v>18</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N87" s="2" t="s">
         <v>28</v>
@@ -5627,7 +5690,7 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>16</v>
@@ -5639,28 +5702,28 @@
         <v>18</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>316</v>
+        <v>222</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>25</v>
+        <v>121</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M88" s="2" t="s">
         <v>27</v>
@@ -5674,7 +5737,7 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>16</v>
@@ -5686,28 +5749,28 @@
         <v>18</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>316</v>
+        <v>222</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M89" s="2" t="s">
         <v>27</v>
@@ -5721,10 +5784,10 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>17</v>
@@ -5733,28 +5796,28 @@
         <v>18</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>316</v>
+        <v>222</v>
       </c>
       <c r="K90" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M90" s="2" t="s">
         <v>27</v>
@@ -5768,40 +5831,40 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>237</v>
+        <v>345</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>316</v>
+        <v>222</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>25</v>
+        <v>162</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M91" s="2" t="s">
         <v>27</v>
@@ -5815,37 +5878,37 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>326</v>
+        <v>214</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>330</v>
+        <v>121</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>25</v>
+        <v>121</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>26</v>
@@ -5854,7 +5917,7 @@
         <v>27</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="O92" s="2" t="s">
         <v>29</v>
@@ -5862,10 +5925,10 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>16</v>
+        <v>301</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>17</v>
@@ -5874,31 +5937,31 @@
         <v>18</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>283</v>
+        <v>27</v>
       </c>
       <c r="N93" s="2" t="s">
         <v>38</v>
@@ -5909,10 +5972,10 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>16</v>
+        <v>301</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>17</v>
@@ -5921,31 +5984,31 @@
         <v>18</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>283</v>
+        <v>27</v>
       </c>
       <c r="N94" s="2" t="s">
         <v>38</v>
@@ -5956,10 +6019,10 @@
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>16</v>
+        <v>301</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>17</v>
@@ -5968,31 +6031,31 @@
         <v>18</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>283</v>
+        <v>27</v>
       </c>
       <c r="N95" s="2" t="s">
         <v>38</v>
@@ -6003,10 +6066,10 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>16</v>
+        <v>301</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>17</v>
@@ -6015,31 +6078,31 @@
         <v>18</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>283</v>
+        <v>27</v>
       </c>
       <c r="N96" s="2" t="s">
         <v>38</v>
@@ -6050,10 +6113,10 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>16</v>
+        <v>301</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>17</v>
@@ -6062,31 +6125,31 @@
         <v>18</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>283</v>
+        <v>27</v>
       </c>
       <c r="N97" s="2" t="s">
         <v>38</v>
@@ -6108,23 +6171,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="B2" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="D2" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="E2" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -6132,16 +6195,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6149,23 +6212,23 @@
         <v>96</v>
       </c>
       <c r="D5" s="5">
-        <v>0.09090909090909091</v>
+        <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>-1.57</v>
+        <v>17.38</v>
       </c>
       <c r="J5" s="4">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="K22">
         <v>56</v>
@@ -6181,7 +6244,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -6212,12 +6275,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="B2">
         <v>96</v>
@@ -6225,41 +6288,41 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>0.09090909090909091</v>
+        <v>0</v>
       </c>
       <c r="B5" s="7"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>-1.57</v>
+        <v>17.38</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>353</v>
+        <v>373</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>354</v>
+        <v>374</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -6267,7 +6330,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -6276,45 +6339,45 @@
         <v>79</v>
       </c>
       <c r="G10" t="s">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>283</v>
+        <v>377</v>
       </c>
       <c r="K10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N10">
         <v>56</v>
       </c>
       <c r="P10" t="s">
-        <v>58</v>
+        <v>223</v>
       </c>
       <c r="Q10">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B11">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E11">
         <v>10</v>
       </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H11">
         <v>31</v>
@@ -6323,30 +6386,30 @@
         <v>27</v>
       </c>
       <c r="K11">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="M11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N11">
         <v>22</v>
       </c>
       <c r="P11" t="s">
-        <v>205</v>
+        <v>28</v>
       </c>
       <c r="Q11">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="E12">
         <v>4</v>
@@ -6358,71 +6421,71 @@
         <v>64</v>
       </c>
       <c r="J12" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="K12">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="N12">
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>28</v>
+        <v>351</v>
       </c>
       <c r="Q12">
-        <v>51</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="E13">
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N13">
         <v>3</v>
       </c>
       <c r="P13" t="s">
-        <v>331</v>
+        <v>38</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D14" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -6433,22 +6496,16 @@
       <c r="N14">
         <v>10</v>
       </c>
-      <c r="P14" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q14">
-        <v>8</v>
-      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>301</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M15" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="N15">
         <v>3</v>
@@ -6456,13 +6513,13 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M16" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -6470,13 +6527,13 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M17" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -6484,29 +6541,29 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>288</v>
+        <v>41</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>264</v>
+        <v>168</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>326</v>
+        <v>153</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>0</v>
@@ -6515,150 +6572,186 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="2">
+        <v>2</v>
+      </c>
       <c r="D21" s="2" t="s">
-        <v>302</v>
+        <v>30</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F21" s="2">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="2">
+        <v>2</v>
+      </c>
       <c r="D22" s="2" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="2">
+        <v>2</v>
+      </c>
       <c r="D23" s="2" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B24" s="2">
+        <v>2</v>
+      </c>
       <c r="D24" s="2" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B25" s="2">
+        <v>2</v>
+      </c>
       <c r="D25" s="2" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="2">
+        <v>1</v>
+      </c>
       <c r="D26" s="2" t="s">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>70</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>79</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>88</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>92</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
